--- a/artfynd/A 6086-2026 artfynd.xlsx
+++ b/artfynd/A 6086-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>76282987</v>
+        <v>128883934</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väster om Sund-Julo NR, Upl</t>
+          <t>Långgärdet, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653008.1618759369</v>
+        <v>653003</v>
       </c>
       <c r="R2" t="n">
-        <v>6711943.028498271</v>
+        <v>6711905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,64 +764,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>76282986</v>
+        <v>128883933</v>
       </c>
       <c r="B3" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3674</v>
+        <v>445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väster om Sund-Julo NR, Upl</t>
+          <t>Långgärdet, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652977.1621057454</v>
+        <v>653008</v>
       </c>
       <c r="R3" t="n">
-        <v>6711917.062883006</v>
+        <v>6711907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,38 +859,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>ÅGP Kalkbarrskog, C-län</t>
-        </is>
-      </c>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>76282990</v>
+        <v>76282989</v>
       </c>
       <c r="B4" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,25 +888,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653008.8975177859</v>
+        <v>653010</v>
       </c>
       <c r="R4" t="n">
-        <v>6711948.976144976</v>
+        <v>6711950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2018-10-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76282989</v>
+        <v>76282986</v>
       </c>
       <c r="B5" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1068,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653009.8417219943</v>
+        <v>652977</v>
       </c>
       <c r="R5" t="n">
-        <v>6711950.00223607</v>
+        <v>6711917</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1051,9 @@
           <t>2018-10-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-10-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1085,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128883931</v>
+        <v>76282990</v>
       </c>
       <c r="B6" t="n">
-        <v>92861</v>
+        <v>87309</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,34 +1096,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>3674</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grönö, Upl</t>
+          <t>Väster om Sund-Julo NR, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>653026</v>
+        <v>653009</v>
       </c>
       <c r="R6" t="n">
-        <v>6711962</v>
+        <v>6711949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,63 +1167,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128883936</v>
+        <v>76282992</v>
       </c>
       <c r="B7" t="n">
-        <v>92817</v>
+        <v>87146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>3762</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långgärdet, Upl</t>
+          <t>Väster om Sund-Julo NR, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652977</v>
+        <v>653010</v>
       </c>
       <c r="R7" t="n">
-        <v>6711883</v>
+        <v>6711992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,12 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,67 +1272,68 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128883933</v>
+        <v>128883936</v>
       </c>
       <c r="B8" t="n">
-        <v>86890</v>
+        <v>93189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>445</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Brandrud</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långgärdet, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>653008</v>
+        <v>652977</v>
       </c>
       <c r="R8" t="n">
-        <v>6711907</v>
+        <v>6711883</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,45 +1392,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128883935</v>
+        <v>76282984</v>
       </c>
       <c r="B9" t="n">
-        <v>92837</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långgärdet, Upl</t>
+          <t>Väster om Sund-Julo NR, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652997</v>
+        <v>652953</v>
       </c>
       <c r="R9" t="n">
-        <v>6711902</v>
+        <v>6711897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2018-10-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1519,28 +1473,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128883934</v>
+        <v>128883935</v>
       </c>
       <c r="B10" t="n">
-        <v>86848</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,38 +1507,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>427</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långgärdet, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>653003</v>
+        <v>652997</v>
       </c>
       <c r="R10" t="n">
-        <v>6711905</v>
+        <v>6711902</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1596,7 @@
         <v>128883932</v>
       </c>
       <c r="B11" t="n">
-        <v>92498</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,6 +1687,297 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128883931</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grönö, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>653026</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6711962</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>76282987</v>
+      </c>
+      <c r="B13" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Väster om Sund-Julo NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>653008</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6711943</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>76282985</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Väster om Sund-Julo NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>652962</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6711899</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-10-04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6086-2026 artfynd.xlsx
+++ b/artfynd/A 6086-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883934</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883933</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282989</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>ÅGP Kalkbarrskog, C-län</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282986</t>
         </is>
       </c>
     </row>
@@ -1187,6 +1212,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282990</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282992</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883936</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
           <t>ÅGP Kalkbarrskog, C-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282984</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883935</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883932</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128883931</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282987</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,8 +2043,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76282985</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>